--- a/coordinates.xlsx
+++ b/coordinates.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="الإحداثيات" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="GIS" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="27">
   <si>
     <t xml:space="preserve">ت</t>
   </si>
@@ -83,6 +84,24 @@
   </si>
   <si>
     <t xml:space="preserve">المجموع الكلي للمساحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area_Dunum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point_No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northing</t>
   </si>
 </sst>
 </file>
@@ -206,8 +225,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -229,6 +252,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -486,1733 +517,1733 @@
   <dimension ref="A1:H103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="n">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="n">
         <v>625</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>3827560</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>465176</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>3827907</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>464694</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>3828473</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>464843</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>3828680</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>463503</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>3828063</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>463697</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>3828099</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>463758</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>3827823</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>463875</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>3827167</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>463912</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>3827179</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>464934</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="n">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="n">
         <v>551</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="n">
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>3867055</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>463193</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>3866640</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>463560</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>3865977</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>464540</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>3866510</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>463800</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>3866061</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>464653</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>3865915</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>464844</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>3865754</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>464770</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>3864930</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>465680</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>3864950</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>465870</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>3864720</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="3" t="n">
         <v>466275</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" s="2" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>3864780</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <v>466485</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>3865680</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="3" t="n">
         <v>465565</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>3866411</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>464669</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>3867000</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="3" t="n">
         <v>463750</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>3867262</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>463507</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>3866102</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>464397</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2" t="n">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G28" s="3" t="n">
         <v>3892221</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="3" t="n">
         <v>347786</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G29" s="3" t="n">
         <v>3893409</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="3" t="n">
         <v>348726</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G30" s="3" t="n">
         <v>3893891</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="3" t="n">
         <v>348377</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G31" s="3" t="n">
         <v>3893408</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="3" t="n">
         <v>347525</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2" t="n">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="n">
         <v>1180</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" s="3" t="n">
         <v>3868845</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="3" t="n">
         <v>354534</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G33" s="3" t="n">
         <v>3869527</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="3" t="n">
         <v>354912</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G34" s="3" t="n">
         <v>3869308</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="3" t="n">
         <v>356898</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G35" s="3" t="n">
         <v>3868749</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="3" t="n">
         <v>356863</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G36" s="3" t="n">
         <v>3868451</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="3" t="n">
         <v>356785</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G37" s="3" t="n">
         <v>3867864</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="3" t="n">
         <v>356803</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G38" s="3" t="n">
         <v>3868151</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="3" t="n">
         <v>354883</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2" t="n">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G39" s="3" t="n">
         <v>3836207</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="3" t="n">
         <v>383594</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G40" s="3" t="n">
         <v>3836746</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="3" t="n">
         <v>384828</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G41" s="3" t="n">
         <v>3835892</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="3" t="n">
         <v>385115</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G42" s="3" t="n">
         <v>3835628</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="3" t="n">
         <v>385074</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G43" s="3" t="n">
         <v>3835399</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="3" t="n">
         <v>383844</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2" t="n">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3" t="n">
         <v>556</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G44" s="3" t="n">
         <v>3815411</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="3" t="n">
         <v>392299</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G45" s="3" t="n">
         <v>3814470</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="3" t="n">
         <v>392635</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" s="3" t="n">
         <v>3814950</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="3" t="n">
         <v>393975</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <v>3815893</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="3" t="n">
         <v>393643</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2" t="n">
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3" t="n">
         <v>4560</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="3" t="n">
         <v>3784175</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="3" t="n">
         <v>381005</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G49" s="3" t="n">
         <v>3785644</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="3" t="n">
         <v>384600</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <v>3783000</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="3" t="n">
         <v>385907</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <v>3781512</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="3" t="n">
         <v>382243</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2" t="n">
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3" t="n">
         <v>791</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="3" t="n">
         <v>3914068</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="3" t="n">
         <v>344673</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G53" s="3" t="n">
         <v>3913363</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="3" t="n">
         <v>343341</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="3" t="n">
         <v>3916168</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="3" t="n">
         <v>342267</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="3" t="n">
         <v>3916869</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="3" t="n">
         <v>343604</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2" t="n">
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <v>3768187</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="3" t="n">
         <v>454510</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <v>3768609</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="3" t="n">
         <v>404710</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="3" t="n">
         <v>3768702</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="3" t="n">
         <v>403719</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="3" t="n">
         <v>3768702</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="3" t="n">
         <v>403427</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G60" s="3" t="n">
         <v>3768747</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="3" t="n">
         <v>403330</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2" t="n">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="3" t="n">
         <v>378800</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="3" t="n">
         <v>403237</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2" t="n">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="3" t="n">
         <v>3768943</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="3" t="n">
         <v>403288</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="3" t="n">
         <v>3769018</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="3" t="n">
         <v>403121</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2" t="n">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G64" s="3" t="n">
         <v>3799649</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="3" t="n">
         <v>403531</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2" t="n">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="3" t="n">
         <v>3799649</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="3" t="n">
         <v>403900</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="A66" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2" t="n">
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3" t="n">
         <v>573</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="3" t="n">
         <v>3839061</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="3" t="n">
         <v>472370</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G67" s="3" t="n">
         <v>3838908</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="3" t="n">
         <v>472553</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2" t="n">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G68" s="3" t="n">
         <v>3838996</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="3" t="n">
         <v>472724</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2" t="n">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G69" s="3" t="n">
         <v>3839169</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="3" t="n">
         <v>472922</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G70" s="3" t="n">
         <v>3839349</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="3" t="n">
         <v>472006</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G71" s="3" t="n">
         <v>3839457</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="3" t="n">
         <v>472131</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2" t="n">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G72" s="3" t="n">
         <v>3839449</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="3" t="n">
         <v>472231</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2" t="n">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G73" s="3" t="n">
         <v>3839435</v>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="3" t="n">
         <v>472235</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2" t="n">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G74" s="3" t="n">
         <v>3839171</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="3" t="n">
         <v>472300</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G75" s="3" t="n">
         <v>3839384</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="3" t="n">
         <v>472407</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G76" s="2" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G76" s="3" t="n">
         <v>3839346</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="3" t="n">
         <v>472546</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G77" s="3" t="n">
         <v>3839384</v>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="3" t="n">
         <v>472587</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G78" s="3" t="n">
         <v>3839376</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="3" t="n">
         <v>472685</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" s="3" t="n">
         <v>3839297</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="3" t="n">
         <v>472647</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G80" s="3" t="n">
         <v>3839104</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="3" t="n">
         <v>472703</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G81" s="3" t="n">
         <v>3838930</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="3" t="n">
         <v>472980</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G82" s="3" t="n">
         <v>3838980</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="3" t="n">
         <v>473090</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G83" s="3" t="n">
         <v>3838927</v>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="3" t="n">
         <v>473081</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="G84" s="3" t="n">
         <v>3838867</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="3" t="n">
         <v>473101</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G85" s="3" t="n">
         <v>3838830</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="3" t="n">
         <v>473151</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2" t="n">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="G86" s="3" t="n">
         <v>3838797</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="3" t="n">
         <v>473015</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2" t="n">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G87" s="3" t="n">
         <v>3838745</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="3" t="n">
         <v>472856</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G88" s="3" t="n">
         <v>3838697</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="3" t="n">
         <v>472766</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G89" s="3" t="n">
         <v>3838660</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="3" t="n">
         <v>472659</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2" t="n">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G90" s="3" t="n">
         <v>3838274</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="3" t="n">
         <v>472959</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2" t="n">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G91" s="3" t="n">
         <v>3838303</v>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="3" t="n">
         <v>473016</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="G92" s="3" t="n">
         <v>3838170</v>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="3" t="n">
         <v>473206</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2" t="n">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G93" s="3" t="n">
         <v>3838065</v>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="3" t="n">
         <v>473245</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2" t="n">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G94" s="2" t="n">
+      <c r="G94" s="3" t="n">
         <v>3837930</v>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="3" t="n">
         <v>473408</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2" t="n">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="G95" s="3" t="n">
         <v>3837887</v>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="3" t="n">
         <v>473398</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2" t="n">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G96" s="2" t="n">
+      <c r="G96" s="3" t="n">
         <v>3837714</v>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="3" t="n">
         <v>473110</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2" t="n">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G97" s="2" t="n">
+      <c r="G97" s="3" t="n">
         <v>3838188</v>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="3" t="n">
         <v>472396</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2" t="n">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G98" s="2" t="n">
+      <c r="G98" s="3" t="n">
         <v>3838201</v>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="3" t="n">
         <v>472367</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2" t="n">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="G99" s="2" t="n">
+      <c r="G99" s="3" t="n">
         <v>3838362</v>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="3" t="n">
         <v>472123</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2" t="n">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G100" s="2" t="n">
+      <c r="G100" s="3" t="n">
         <v>3838762</v>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="3" t="n">
         <v>471522</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2" t="n">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="G101" s="2" t="n">
+      <c r="G101" s="3" t="n">
         <v>3838797</v>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="3" t="n">
         <v>471470</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2" t="n">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="G102" s="2" t="n">
+      <c r="G102" s="3" t="n">
         <v>3838835</v>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="3" t="n">
         <v>471424</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4"/>
-      <c r="B103" s="5" t="s">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5"/>
+      <c r="B103" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="5" t="n">
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="6" t="n">
         <f aca="false">SUM(E2:E102)</f>
         <v>10558</v>
       </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -2275,4 +2306,2050 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>465176</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>3827560</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>464694</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>3827907</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>464843</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>3828473</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>463503</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>3828680</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>463697</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>3828063</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>463758</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>3828099</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>463875</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>3827823</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>463912</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>3827167</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>625</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>464934</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>3827179</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>463193</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>3867055</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>463560</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>3866640</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>464540</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>3865977</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>463800</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>3866510</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>464653</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>3866061</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>464844</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>3865915</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>464770</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>3865754</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>465680</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>3864930</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>465870</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>3864950</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>466275</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>3864720</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>466485</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>3864780</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>465565</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>3865680</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>464669</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>3866411</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>463750</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>3867000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>463507</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>3867262</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>464397</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>3866102</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>347786</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>3892221</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>348726</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>3893409</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>348377</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>3893891</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>347525</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>3893408</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>354534</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>3868845</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>354912</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>3869527</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>356898</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>3869308</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>356863</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>3868749</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>356785</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>3868451</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>356803</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>3867864</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>354883</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>3868151</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>383594</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>3836207</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>384828</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>3836746</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>385115</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>3835892</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>385074</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>3835628</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>383844</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>3835399</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>392299</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>3815411</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>392635</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>3814470</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>393975</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>3814950</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>556</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>393643</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>3815893</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>4560</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>381005</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>3784175</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>4560</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>384600</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>3785644</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>4560</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>385907</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>3783000</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>4560</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>382243</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>3781512</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>791</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>344673</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>3914068</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>791</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>343341</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>3913363</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>791</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>342267</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>3916168</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>791</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>343604</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>3916869</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>454510</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>3768187</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>404710</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>3768609</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>403719</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>3768702</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>403427</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>3768702</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>403330</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>3768747</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>403237</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>378800</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>403288</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>3768943</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>403121</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>3769018</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>403531</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>3799649</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>372</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>403900</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>3799649</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>472370</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>3839061</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>472553</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>3838908</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>472724</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>3838996</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>472922</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>3839169</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>472006</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>3839349</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>472131</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>3839457</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>472231</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>3839449</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>472235</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>3839435</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>472300</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>3839171</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>472407</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>3839384</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>472546</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>3839346</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>472587</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>3839384</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>472685</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>3839376</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>472647</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>3839297</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>472703</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>3839104</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>472980</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>3838930</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>473090</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>3838980</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>473081</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>3838927</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>473101</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>3838867</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>473151</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>3838830</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>473015</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>3838797</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>472856</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>3838745</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>472766</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>3838697</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>472659</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>3838660</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>472959</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>3838274</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>473016</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>3838303</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>473206</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>3838170</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>473245</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>3838065</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>473408</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>3837930</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>473398</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>3837887</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>473110</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>3837714</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D96" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>472396</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>3838188</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>472367</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>3838201</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D98" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>472123</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>3838362</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D99" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>471522</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>3838762</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D100" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>471470</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>3838797</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="8" t="n">
+        <v>573</v>
+      </c>
+      <c r="D101" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>471424</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>3838835</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>